--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>a</t>
   </si>
@@ -38,7 +38,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
+    <t>&lt;sprite=1&gt;守护</t>
   </si>
   <si>
     <t>c</t>
@@ -92,9 +92,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>&lt;sprite=1&gt;守护</t>
-  </si>
-  <si>
     <t>g</t>
   </si>
   <si>
@@ -125,195 +122,198 @@
     <t>8</t>
   </si>
   <si>
+    <t>&lt;sprite=0&gt;若这是你的最后两张手牌，减速</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>闪电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;连击</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中一张其它法术进入冷却，获得连击</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>磁暴</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+3</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域加速</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>引雷</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于6的法术获得连击（不能叠加）</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>过载</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>海涌</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>水刃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>喷泉</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>荆棘</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;双发</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，此法术冷却时间减2</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>飞叶连击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;此法术获得的额外进攻力量翻倍</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，获得减速</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量&gt;=7则立即进入冷却且冷却时间减一</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却等于3且无光环 的法术的力量和进攻效果</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;未复制或其他情况下力量视为1</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>瀑流</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你每损失一点生命值（相较初始值），额外加速一个不同的法术</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>地动波</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>漩涡</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;可以将你的冷却区中的一张法术永久移出游戏，获得 加速×3</t>
+  </si>
+  <si>
+    <t>ab</t>
+  </si>
+  <si>
+    <t>湍流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;加速×2</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>雪球</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你的冷却区每有一张牌，进攻力量+1</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>雷云</t>
+  </si>
+  <si>
     <t>&lt;sprite=0&gt;减速</t>
   </si>
   <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>闪电</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;连击</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>电弧</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中一张其它法术进入冷却，获得连击</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>磁暴</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+3</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域加速</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>引雷</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于6的法术获得连击（不能叠加）</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>过载</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>自燃</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>海涌</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>水刃</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>喷泉</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>荆棘</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;双发</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，此法术冷却时间减2</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>飞叶连击</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;此法术获得的额外进攻力量翻倍</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，获得减速</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量&gt;=7则立即进入冷却且冷却时间减一</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却等于3且无光环 的法术的力量和进攻效果</t>
-  </si>
-  <si>
-    <t>&lt;sprite=2&gt;未复制或其他情况下力量视为1</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>瀑流</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;你每损失一点生命值（相较初始值），额外加速一个不同的法术</t>
-  </si>
-  <si>
-    <t>z</t>
-  </si>
-  <si>
-    <t>地动波</t>
-  </si>
-  <si>
-    <t>aa</t>
-  </si>
-  <si>
-    <t>漩涡</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;可以将你的冷却区中的一张法术永久移出游戏，获得 加速×3</t>
-  </si>
-  <si>
-    <t>ab</t>
-  </si>
-  <si>
-    <t>湍流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;加速×2</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>雪球</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;你的冷却区每有一张牌，进攻力量+1</t>
-  </si>
-  <si>
-    <t>ad</t>
-  </si>
-  <si>
-    <t>雷云</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却</t>
   </si>
   <si>
@@ -405,93 +405,6 @@
   </si>
   <si>
     <t>&lt;sprite=0&gt;可以选择使自己和对方的 冷却区中剩余冷却为1的法术 都被减速</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>次声波</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;强化×2（只会获得一次力量加成，但是叠加两点强化值）</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;强化</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>共振</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;强化</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+当前强化值</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>振荡</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>剧毒种子</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;中毒×2</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>毒刺</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;中毒</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>裂变</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;若 这是你手中最后一张法术 并且 是本回合打出的第一张法术，则进攻结束后再开始一次你的进攻回合</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>鬼火</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;你的生命值 小于等于初始值的一半 时，进攻力量+1</t>
-  </si>
-  <si>
-    <t>&lt;sprite=2&gt;你的生命值减少时，此法术立即冷却完毕</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>雾隐</t>
-  </si>
-  <si>
-    <t>&lt;sprite=2&gt;此法术冷却完毕时，立即获得加速×2</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>电力转换</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;可以将手中一张其它法术进入冷却，然后获得连击</t>
   </si>
 </sst>
 </file>
@@ -537,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,16 +563,13 @@
       <c r="E6" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>27</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>28</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>25</v>
@@ -668,15 +578,15 @@
         <v>2</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>31</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>16</v>
@@ -685,52 +595,52 @@
         <v>11</v>
       </c>
       <c r="E8" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="0" t="s">
         <v>32</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="C9" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="D9" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="0" t="s">
         <v>36</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="C10" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>42</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>11</v>
@@ -739,35 +649,35 @@
         <v>12</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="C12" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="F12" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="0" t="s">
         <v>47</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>48</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>20</v>
@@ -776,35 +686,35 @@
         <v>2</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="C14" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="0" t="s">
         <v>51</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="0" t="s">
         <v>53</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>54</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>20</v>
@@ -813,18 +723,18 @@
         <v>2</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>56</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>57</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>12</v>
@@ -833,18 +743,18 @@
         <v>12</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>58</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>59</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>2</v>
@@ -856,15 +766,15 @@
         <v>3</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="0" t="s">
         <v>60</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>61</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>7</v>
@@ -873,16 +783,16 @@
         <v>11</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>64</v>
-      </c>
       <c r="C19" s="0" t="s">
         <v>11</v>
       </c>
@@ -890,38 +800,38 @@
         <v>11</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="C20" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="F20" s="0" t="s">
         <v>67</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>69</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>70</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>12</v>
@@ -930,18 +840,18 @@
         <v>12</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>72</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>73</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>7</v>
@@ -950,18 +860,18 @@
         <v>11</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="0" t="s">
         <v>75</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>76</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>12</v>
@@ -970,41 +880,41 @@
         <v>11</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="C24" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="D24" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="F24" s="0" t="s">
         <v>81</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="C25" s="0" t="s">
         <v>84</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>85</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>11</v>
@@ -1013,15 +923,15 @@
         <v>3</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>87</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>88</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>16</v>
@@ -1030,7 +940,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>22</v>
@@ -1038,10 +948,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="0" t="s">
         <v>89</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>90</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>2</v>
@@ -1050,15 +960,15 @@
         <v>12</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>92</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>93</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>7</v>
@@ -1067,15 +977,15 @@
         <v>11</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>95</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>96</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>2</v>
@@ -1084,24 +994,24 @@
         <v>12</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="C30" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="0" t="s">
         <v>99</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>37</v>
       </c>
       <c r="F30" s="0" t="s">
         <v>100</v>
@@ -1158,7 +1068,7 @@
         <v>11</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="F33" s="0" t="s">
         <v>109</v>
@@ -1192,7 +1102,7 @@
         <v>114</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>11</v>
@@ -1209,7 +1119,7 @@
         <v>117</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>2</v>
@@ -1229,7 +1139,7 @@
         <v>120</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>2</v>
@@ -1238,7 +1148,7 @@
         <v>121</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -1249,7 +1159,7 @@
         <v>123</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>2</v>
@@ -1258,7 +1168,7 @@
         <v>124</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -1289,187 +1199,13 @@
         <v>129</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="F49" s="0" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>a</t>
   </si>
@@ -254,10 +254,10 @@
     <t>X</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却等于3且无光环 的法术的力量和进攻效果</t>
-  </si>
-  <si>
-    <t>&lt;sprite=2&gt;未复制或其他情况下力量视为1</t>
+    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却&lt;=3且无光环 的法术的力量和进攻效果</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;未复制或防御时力量视为1</t>
   </si>
   <si>
     <t>y</t>
@@ -284,7 +284,7 @@
     <t>漩涡</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;可以将你的冷却区中的一张法术永久移出游戏，获得 加速×3</t>
+    <t>&lt;sprite=0&gt;光环：使一个法术获得快速回填</t>
   </si>
   <si>
     <t>ab</t>
@@ -405,6 +405,27 @@
   </si>
   <si>
     <t>&lt;sprite=0&gt;可以选择使自己和对方的 冷却区中剩余冷却为1的法术 都被减速</t>
+  </si>
+  <si>
+    <t>ao</t>
+  </si>
+  <si>
+    <t>冰川核心</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使对方下次进攻时，法术最终的力量值减半（向上取整）</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>火炬</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;每当你生命值减少时，此光环将恢复到可用状态</t>
   </si>
 </sst>
 </file>
@@ -450,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,7 +798,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>11</v>
@@ -954,12 +975,15 @@
         <v>89</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="0" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1206,6 +1230,46 @@
       </c>
       <c r="E40" s="0" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -410,7 +410,7 @@
     <t>ao</t>
   </si>
   <si>
-    <t>冰川核心</t>
+    <t>冰霜核心</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;使对方下次进攻时，法术最终的力量值减半（向上取整）</t>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t>a</t>
   </si>
@@ -308,124 +308,139 @@
     <t>ad</t>
   </si>
   <si>
+    <t>吞食</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却</t>
+  </si>
+  <si>
+    <t>ae</t>
+  </si>
+  <si>
+    <t>灼烧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你或对方每损失一点生命值（相较初始值），都会进攻力量+1</t>
+  </si>
+  <si>
+    <t>af</t>
+  </si>
+  <si>
+    <t>冰封铠甲</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带防御力量+2</t>
+  </si>
+  <si>
+    <t>ag</t>
+  </si>
+  <si>
+    <t>淬火</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
+  </si>
+  <si>
+    <t>ah</t>
+  </si>
+  <si>
+    <t>烈焰斗篷</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3或防御力量+3</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>爆燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+4</t>
+  </si>
+  <si>
+    <t>aj</t>
+  </si>
+  <si>
+    <t>火灾</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+1</t>
+  </si>
+  <si>
+    <t>ak</t>
+  </si>
+  <si>
+    <t>石化</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：免疫力量大于等于6的攻击（包括双发）</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>石盾</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：免疫力量小于等于3的攻击（包括双发）</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>充能</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一次加速</t>
+  </si>
+  <si>
+    <t>an</t>
+  </si>
+  <si>
+    <t>雪崩</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;可以选择使自己和对方的 冷却区中剩余冷却为1的法术 都被减速</t>
+  </si>
+  <si>
+    <t>ao</t>
+  </si>
+  <si>
+    <t>冰霜核心</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使对方下次进攻时，法术最终的力量值减半（向上取整）</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>火炬</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;每当你生命值减少时，此光环将恢复到可用状态</t>
+  </si>
+  <si>
+    <t>aq</t>
+  </si>
+  <si>
     <t>雷云</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;减速</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却</t>
-  </si>
-  <si>
-    <t>ae</t>
-  </si>
-  <si>
-    <t>灼烧</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;你或对方每损失一点生命值（相较初始值），都会进攻力量+1</t>
-  </si>
-  <si>
-    <t>af</t>
-  </si>
-  <si>
-    <t>冰封铠甲</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带防御力量+2</t>
-  </si>
-  <si>
-    <t>ag</t>
-  </si>
-  <si>
-    <t>淬火</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
-  </si>
-  <si>
-    <t>ah</t>
-  </si>
-  <si>
-    <t>烈焰斗篷</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3或防御力量+3</t>
-  </si>
-  <si>
-    <t>ai</t>
-  </si>
-  <si>
-    <t>爆燃</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+4</t>
-  </si>
-  <si>
-    <t>aj</t>
-  </si>
-  <si>
-    <t>火灾</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+1</t>
-  </si>
-  <si>
-    <t>ak</t>
-  </si>
-  <si>
-    <t>石化</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：免疫力量大于等于6的攻击（包括双发）</t>
-  </si>
-  <si>
-    <t>al</t>
-  </si>
-  <si>
-    <t>石盾</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：免疫力量小于等于3的攻击（包括双发）</t>
-  </si>
-  <si>
-    <t>am</t>
-  </si>
-  <si>
-    <t>充能</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一次加速</t>
-  </si>
-  <si>
-    <t>an</t>
-  </si>
-  <si>
-    <t>雪崩</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;可以选择使自己和对方的 冷却区中剩余冷却为1的法术 都被减速</t>
-  </si>
-  <si>
-    <t>ao</t>
-  </si>
-  <si>
-    <t>冰霜核心</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使对方下次进攻时，法术最终的力量值减半（向上取整）</t>
-  </si>
-  <si>
-    <t>ap</t>
-  </si>
-  <si>
-    <t>火炬</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3</t>
-  </si>
-  <si>
-    <t>&lt;sprite=2&gt;每当你生命值减少时，此光环将恢复到可用状态</t>
+    <t>ar</t>
+  </si>
+  <si>
+    <t>地刺</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;如果这是你手中的最后一张牌，进攻打出之后自动回手</t>
   </si>
 </sst>
 </file>
@@ -471,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1272,6 +1287,43 @@
         <v>137</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
